--- a/etf_holdings/2026-09-04_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-04_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,70 +738,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>台灣塑膠工業</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>台灣塑膠工業</t>
-        </is>
-      </c>
+          <t>譜瑞-KY</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.00%</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.70%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-0.30%</t>
-        </is>
-      </c>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>1577000</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1103000</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-474,000</t>
-        </is>
-      </c>
+        <v>16000</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -816,55 +798,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>東元電機</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>東元電機</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3473000</v>
+        <v>300000</v>
       </c>
       <c r="K7" t="n">
-        <v>2904000</v>
+        <v>191000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-569,000</t>
+          <t>-109,000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -879,55 +861,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>川湖科技</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>川湖科技</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7000</v>
+        <v>3100000</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>1500000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>-1,600,000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -942,55 +924,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>15.99%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>15.47%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>383000</v>
+        <v>10500000</v>
       </c>
       <c r="K9" t="n">
-        <v>295000</v>
+        <v>10300000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-88,000</t>
+          <t>-200,000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1005,55 +987,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>138000</v>
+        <v>2000000</v>
       </c>
       <c r="K10" t="n">
-        <v>97000</v>
+        <v>1000000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-41,000</t>
+          <t>-1,000,000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1068,55 +1050,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>193000</v>
+        <v>5000000</v>
       </c>
       <c r="K11" t="n">
-        <v>105000</v>
+        <v>1500000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-88,000</t>
+          <t>-3,500,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1131,55 +1113,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>富邦金融控股</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>富邦金融控股</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>154000</v>
+        <v>1351000</v>
       </c>
       <c r="K12" t="n">
-        <v>1004000</v>
+        <v>2000000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>850,000</t>
+          <t>649,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1189,53 +1171,53 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>中國信託金融控股</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>中國信託金融控股</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>3.69%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>3.39%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>306000</v>
+        <v>810000</v>
       </c>
       <c r="K13" t="n">
-        <v>2178000</v>
+        <v>736000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1,872,000</t>
+          <t>-74,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1257,43 +1239,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>台灣塑膠工業</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>台灣塑膠工業</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>16000</v>
+        <v>1577000</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>1103000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-15,000</t>
+          <t>-474,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1320,17 +1302,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>奇鋐科技</t>
+          <t>東元電機</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>奇鋐科技</t>
+          <t>東元電機</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1340,23 +1322,23 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.74%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>76000</v>
+        <v>3473000</v>
       </c>
       <c r="K15" t="n">
-        <v>52000</v>
+        <v>2904000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-24,000</t>
+          <t>-569,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1383,43 +1365,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>川湖科技</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>川湖科技</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>31000</v>
+        <v>7000</v>
       </c>
       <c r="K16" t="n">
-        <v>22000</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-9,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1446,43 +1428,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>穩懋半導體</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>穩懋半導體</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>1.97%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>1.46%</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.87%</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>326000</v>
+        <v>383000</v>
       </c>
       <c r="K17" t="n">
-        <v>203000</v>
+        <v>295000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-123,000</t>
+          <t>-88,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1509,43 +1491,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>健策精密工業</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>健策精密工業</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>2.81%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.50%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>27000</v>
+        <v>138000</v>
       </c>
       <c r="K18" t="n">
-        <v>18000</v>
+        <v>97000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-9,000</t>
+          <t>-41,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1572,43 +1554,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>貿聯控股（BizLink Holding In</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>貿聯控股（BizLink Holding In</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="J19" t="n">
+        <v>193000</v>
+      </c>
+      <c r="K19" t="n">
         <v>105000</v>
       </c>
-      <c r="K19" t="n">
-        <v>94000</v>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-11,000</t>
+          <t>-88,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1635,43 +1617,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>日月光投資控股</t>
+          <t>富邦金融控股</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>日月光投資控股</t>
+          <t>富邦金融控股</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.01%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>435000</v>
+        <v>154000</v>
       </c>
       <c r="K20" t="n">
-        <v>706000</v>
+        <v>1004000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>271,000</t>
+          <t>850,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1693,48 +1675,48 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>中國信託金融控股</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>中國信託金融控股</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>110000</v>
+        <v>306000</v>
       </c>
       <c r="K21" t="n">
-        <v>77000</v>
+        <v>2178000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-33,000</t>
+          <t>1,872,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1756,48 +1738,48 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>光紅建聖</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>光紅建聖</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>+1.12%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>74000</v>
+        <v>16000</v>
       </c>
       <c r="K22" t="n">
-        <v>140000</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>-15,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1824,43 +1806,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>環球晶圓</t>
+          <t>奇鋐科技</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>環球晶圓</t>
+          <t>奇鋐科技</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-0.74%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>174000</v>
+        <v>76000</v>
       </c>
       <c r="K23" t="n">
-        <v>143000</v>
+        <v>52000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-31,000</t>
+          <t>-24,000</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1887,43 +1869,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>新代科技</t>
+          <t>聯亞光電工業</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>新代科技</t>
+          <t>聯亞光電工業</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>108000</v>
+        <v>31000</v>
       </c>
       <c r="K24" t="n">
-        <v>92000</v>
+        <v>22000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-16,000</t>
+          <t>-9,000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1950,22 +1932,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>高力熱處理工業</t>
+          <t>穩懋半導體</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>高力熱處理工業</t>
+          <t>穩懋半導體</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1975,18 +1957,18 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>113000</v>
+        <v>326000</v>
       </c>
       <c r="K25" t="n">
-        <v>76000</v>
+        <v>203000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-37,000</t>
+          <t>-123,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1998,7 +1980,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2008,60 +1990,60 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>健策精密工業</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>健策精密工業</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-0.50%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>229675</v>
+        <v>27000</v>
       </c>
       <c r="K26" t="n">
-        <v>429675</v>
+        <v>18000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>-9,000</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-03_00992A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2071,60 +2053,60 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>177000</v>
+        <v>105000</v>
       </c>
       <c r="K27" t="n">
-        <v>277000</v>
+        <v>94000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>-11,000</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2134,60 +2116,60 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>日月光投資控股</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>日月光投資控股</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>4.01%</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>513000</v>
+        <v>435000</v>
       </c>
       <c r="K28" t="n">
-        <v>441000</v>
+        <v>706000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-72,000</t>
+          <t>271,000</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2202,55 +2184,55 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>595000</v>
+        <v>110000</v>
       </c>
       <c r="K29" t="n">
-        <v>485000</v>
+        <v>77000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-110,000</t>
+          <t>-33,000</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2260,60 +2242,60 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>光紅建聖</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>光紅建聖</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>2.39%</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>+1.12%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>979000</v>
+        <v>74000</v>
       </c>
       <c r="K30" t="n">
-        <v>696000</v>
+        <v>140000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-283,000</t>
+          <t>66,000</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2323,105 +2305,123 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>環球晶圓</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>環球晶圓</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>12000</v>
+        <v>174000</v>
       </c>
       <c r="K31" t="n">
-        <v>49000</v>
+        <v>143000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>37,000</t>
+          <t>-31,000</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6510</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>7750</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>新代科技</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>精測</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>新代科技</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2.37%</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.54%</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>1.95%</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>-0.42%</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>108000</v>
+      </c>
       <c r="K32" t="n">
-        <v>16000</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
+        <v>92000</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-16,000</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2431,60 +2431,60 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>高力熱處理工業</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>高力熱處理工業</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>1613000</v>
+        <v>113000</v>
       </c>
       <c r="K33" t="n">
-        <v>1669000</v>
+        <v>76000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>56,000</t>
+          <t>-37,000</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2494,60 +2494,60 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>2.61%</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>1276000</v>
+        <v>229675</v>
       </c>
       <c r="K34" t="n">
-        <v>1241000</v>
+        <v>429675</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-35,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+          <t>2026-09-03_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2562,55 +2562,55 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>161000</v>
+        <v>177000</v>
       </c>
       <c r="K35" t="n">
-        <v>165000</v>
+        <v>277000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2625,55 +2625,55 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>167000</v>
+        <v>513000</v>
       </c>
       <c r="K36" t="n">
-        <v>165000</v>
+        <v>441000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-72,000</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2683,60 +2683,60 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>629000</v>
+        <v>595000</v>
       </c>
       <c r="K37" t="n">
-        <v>637000</v>
+        <v>485000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>-110,000</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2746,60 +2746,60 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.63%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>198000</v>
+        <v>979000</v>
       </c>
       <c r="K38" t="n">
-        <v>200000</v>
+        <v>696000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>-283,000</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2814,48 +2814,48 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>131000</v>
+        <v>12000</v>
       </c>
       <c r="K39" t="n">
-        <v>134000</v>
+        <v>49000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>37,000</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -2867,55 +2867,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2455</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>全新</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>1.67%</t>
-        </is>
-      </c>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.73%</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>+0.06%</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>315000</v>
-      </c>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="n">
-        <v>327000</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>12,000</t>
-        </is>
-      </c>
+        <v>16000</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>2026-09-03_00993A_full_holdings.xlsx</t>
@@ -2935,48 +2917,48 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.72%</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>107000</v>
+        <v>1613000</v>
       </c>
       <c r="K41" t="n">
-        <v>105000</v>
+        <v>1669000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>56,000</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2998,32 +2980,32 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3032,14 +3014,14 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>192000</v>
+        <v>1276000</v>
       </c>
       <c r="K42" t="n">
-        <v>196000</v>
+        <v>1241000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>-35,000</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3066,43 +3048,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>88000</v>
+        <v>161000</v>
       </c>
       <c r="K43" t="n">
-        <v>90000</v>
+        <v>165000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3124,48 +3106,48 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>46000</v>
+        <v>167000</v>
       </c>
       <c r="K44" t="n">
-        <v>47000</v>
+        <v>165000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3192,43 +3174,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>939000</v>
+        <v>629000</v>
       </c>
       <c r="K45" t="n">
-        <v>953000</v>
+        <v>637000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3255,43 +3237,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>556000</v>
+        <v>198000</v>
       </c>
       <c r="K46" t="n">
-        <v>564000</v>
+        <v>200000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3313,48 +3295,48 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>23000</v>
+        <v>131000</v>
       </c>
       <c r="K47" t="n">
-        <v>22000</v>
+        <v>134000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3381,43 +3363,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>1.73%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>352000</v>
+        <v>315000</v>
       </c>
       <c r="K48" t="n">
-        <v>359000</v>
+        <v>327000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3439,48 +3421,48 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>390000</v>
+        <v>107000</v>
       </c>
       <c r="K49" t="n">
-        <v>401000</v>
+        <v>105000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>11,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3502,48 +3484,48 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>信驊科技</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>信驊科技</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-0.76%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>20600</v>
+        <v>192000</v>
       </c>
       <c r="K50" t="n">
-        <v>15600</v>
+        <v>196000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-5,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3570,39 +3552,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>0.44%</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>0.46%</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>163000</v>
+        <v>88000</v>
       </c>
       <c r="K51" t="n">
-        <v>165000</v>
+        <v>90000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3633,43 +3615,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>90000</v>
+        <v>46000</v>
       </c>
       <c r="K52" t="n">
-        <v>93000</v>
+        <v>47000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3691,48 +3673,48 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>34000</v>
+        <v>939000</v>
       </c>
       <c r="K53" t="n">
-        <v>32000</v>
+        <v>953000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>14,000</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3754,48 +3736,48 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>140191</v>
+        <v>556000</v>
       </c>
       <c r="K54" t="n">
-        <v>134191</v>
+        <v>564000</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3817,48 +3799,48 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>勤誠興業</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>勤誠興業</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>67000</v>
+        <v>23000</v>
       </c>
       <c r="K55" t="n">
-        <v>68000</v>
+        <v>22000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3885,46 +3867,550 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>3702</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>大聯大</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>大聯大</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>352000</v>
+      </c>
+      <c r="K56" t="n">
+        <v>359000</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>1.88%</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>390000</v>
+      </c>
+      <c r="K57" t="n">
+        <v>401000</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>信驊科技</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>信驊科技</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2.81%</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>-0.76%</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>20600</v>
+      </c>
+      <c r="K58" t="n">
+        <v>15600</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>-5,000</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>6239</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>0.44%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>163000</v>
+      </c>
+      <c r="K59" t="n">
+        <v>165000</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>矽力*-KY</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>矽力*-KY</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>90000</v>
+      </c>
+      <c r="K60" t="n">
+        <v>93000</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2.34%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>-0.08%</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>34000</v>
+      </c>
+      <c r="K61" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>3.58%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>3.35%</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>140191</v>
+      </c>
+      <c r="K62" t="n">
+        <v>134191</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>-6,000</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>勤誠興業</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>勤誠興業</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>0.65%</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>67000</v>
+      </c>
+      <c r="K63" t="n">
+        <v>68000</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>8996</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>1.51%</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>1.53%</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>+0.02%</t>
         </is>
       </c>
-      <c r="J56" t="n">
+      <c r="J64" t="n">
         <v>122000</v>
       </c>
-      <c r="K56" t="n">
+      <c r="K64" t="n">
         <v>128000</v>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-09-04_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-04_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,55 +627,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>台灣塑膠工業</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>台灣塑膠工業</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1158000</v>
+        <v>1577000</v>
       </c>
       <c r="K4" t="n">
-        <v>1145000</v>
+        <v>1103000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-13,000</t>
+          <t>-474,000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-09-03_00982A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -685,105 +685,123 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>東元電機</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>東元電機</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>103000</v>
+        <v>3473000</v>
       </c>
       <c r="K5" t="n">
-        <v>115000</v>
+        <v>2904000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>-569,000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-09-03_00982A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>川湖科技</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>川湖科技</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.01%</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>0.93%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.13%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-0.80%</t>
+        </is>
+      </c>
       <c r="J6" t="n">
-        <v>16000</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+        <v>7000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-6,000</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-03_00403A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -798,55 +816,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>300000</v>
+        <v>383000</v>
       </c>
       <c r="K7" t="n">
-        <v>191000</v>
+        <v>295000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-109,000</t>
+          <t>-88,000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-09-03_00403A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -861,55 +879,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>長興</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>長興</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>2.81%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3100000</v>
+        <v>138000</v>
       </c>
       <c r="K8" t="n">
-        <v>1500000</v>
+        <v>97000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-1,600,000</t>
+          <t>-41,000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-09-03_00403A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -924,55 +942,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>15.99%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>15.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>10500000</v>
+        <v>193000</v>
       </c>
       <c r="K9" t="n">
-        <v>10300000</v>
+        <v>105000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-200,000</t>
+          <t>-88,000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-09-03_00403A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -982,60 +1000,60 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>富邦金融控股</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>富邦金融控股</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2000000</v>
+        <v>154000</v>
       </c>
       <c r="K10" t="n">
-        <v>1000000</v>
+        <v>1004000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-1,000,000</t>
+          <t>850,000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09-03_00403A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1045,60 +1063,60 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>中國信託金融控股</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>中國信託金融控股</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>5000000</v>
+        <v>306000</v>
       </c>
       <c r="K11" t="n">
-        <v>1500000</v>
+        <v>2178000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-3,500,000</t>
+          <t>1,872,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-03_00403A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1108,60 +1126,60 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1351000</v>
+        <v>16000</v>
       </c>
       <c r="K12" t="n">
-        <v>2000000</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>649,000</t>
+          <t>-15,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-03_00403A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1176,48 +1194,48 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>奇鋐科技</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>奇鋐科技</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.74%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>810000</v>
+        <v>76000</v>
       </c>
       <c r="K13" t="n">
-        <v>736000</v>
+        <v>52000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-74,000</t>
+          <t>-24,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-09-03_00403A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1239,17 +1257,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>台灣塑膠工業</t>
+          <t>聯亞光電工業</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>台灣塑膠工業</t>
+          <t>聯亞光電工業</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1259,23 +1277,23 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1577000</v>
+        <v>31000</v>
       </c>
       <c r="K14" t="n">
-        <v>1103000</v>
+        <v>22000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-474,000</t>
+          <t>-9,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1302,43 +1320,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>東元電機</t>
+          <t>穩懋半導體</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>東元電機</t>
+          <t>穩懋半導體</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3473000</v>
+        <v>326000</v>
       </c>
       <c r="K15" t="n">
-        <v>2904000</v>
+        <v>203000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-569,000</t>
+          <t>-123,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1365,43 +1383,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>川湖科技</t>
+          <t>健策精密工業</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>川湖科技</t>
+          <t>健策精密工業</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>-0.50%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>7000</v>
+        <v>27000</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>18000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>-9,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1428,43 +1446,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>383000</v>
+        <v>105000</v>
       </c>
       <c r="K17" t="n">
-        <v>295000</v>
+        <v>94000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-88,000</t>
+          <t>-11,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1486,48 +1504,48 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>日月光投資控股</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>日月光投資控股</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>4.01%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>138000</v>
+        <v>435000</v>
       </c>
       <c r="K18" t="n">
-        <v>97000</v>
+        <v>706000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-41,000</t>
+          <t>271,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1554,43 +1572,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>193000</v>
+        <v>110000</v>
       </c>
       <c r="K19" t="n">
-        <v>105000</v>
+        <v>77000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-88,000</t>
+          <t>-33,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1617,43 +1635,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>富邦金融控股</t>
+          <t>光紅建聖</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>富邦金融控股</t>
+          <t>光紅建聖</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>2.39%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+1.12%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>154000</v>
+        <v>74000</v>
       </c>
       <c r="K20" t="n">
-        <v>1004000</v>
+        <v>140000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>850,000</t>
+          <t>66,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1675,48 +1693,48 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>中國信託金融控股</t>
+          <t>環球晶圓</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>中國信託金融控股</t>
+          <t>環球晶圓</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>306000</v>
+        <v>174000</v>
       </c>
       <c r="K21" t="n">
-        <v>2178000</v>
+        <v>143000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1,872,000</t>
+          <t>-31,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1743,43 +1761,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>新代科技</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>新代科技</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>2.37%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>16000</v>
+        <v>108000</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>92000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-15,000</t>
+          <t>-16,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1806,43 +1824,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>奇鋐科技</t>
+          <t>高力熱處理工業</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>奇鋐科技</t>
+          <t>高力熱處理工業</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.74%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="J23" t="n">
+        <v>113000</v>
+      </c>
+      <c r="K23" t="n">
         <v>76000</v>
       </c>
-      <c r="K23" t="n">
-        <v>52000</v>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-24,000</t>
+          <t>-37,000</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1854,7 +1872,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1864,60 +1882,60 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>2.61%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>31000</v>
+        <v>229675</v>
       </c>
       <c r="K24" t="n">
-        <v>22000</v>
+        <v>429675</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-9,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,60 +1945,60 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>穩懋半導體</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>穩懋半導體</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>326000</v>
+        <v>177000</v>
       </c>
       <c r="K25" t="n">
-        <v>203000</v>
+        <v>277000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-123,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1995,55 +2013,55 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>健策精密工業</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>健策精密工業</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-0.50%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>27000</v>
+        <v>513000</v>
       </c>
       <c r="K26" t="n">
-        <v>18000</v>
+        <v>441000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-9,000</t>
+          <t>-72,000</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2058,55 +2076,55 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>貿聯控股（BizLink Holding In</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>貿聯控股（BizLink Holding In</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>105000</v>
+        <v>595000</v>
       </c>
       <c r="K27" t="n">
-        <v>94000</v>
+        <v>485000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-11,000</t>
+          <t>-110,000</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2116,60 +2134,60 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>日月光投資控股</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>日月光投資控股</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.01%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-0.63%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>435000</v>
+        <v>979000</v>
       </c>
       <c r="K28" t="n">
-        <v>706000</v>
+        <v>696000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>271,000</t>
+          <t>-283,000</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2179,123 +2197,105 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>110000</v>
+        <v>12000</v>
       </c>
       <c r="K29" t="n">
-        <v>77000</v>
+        <v>49000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-33,000</t>
+          <t>37,000</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6442</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>光紅建聖</t>
-        </is>
-      </c>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>光紅建聖</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>1.27%</t>
-        </is>
-      </c>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2.39%</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>+1.12%</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>74000</v>
-      </c>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
-        <v>140000</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>66,000</t>
-        </is>
-      </c>
+        <v>16000</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2305,60 +2305,60 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>環球晶圓</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>環球晶圓</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>3.72%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>174000</v>
+        <v>1613000</v>
       </c>
       <c r="K31" t="n">
-        <v>143000</v>
+        <v>1669000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-31,000</t>
+          <t>56,000</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2373,55 +2373,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>新代科技</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>新代科技</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>108000</v>
+        <v>1276000</v>
       </c>
       <c r="K32" t="n">
-        <v>92000</v>
+        <v>1241000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-16,000</t>
+          <t>-35,000</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2431,60 +2431,60 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>高力熱處理工業</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>高力熱處理工業</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>113000</v>
+        <v>161000</v>
       </c>
       <c r="K33" t="n">
-        <v>76000</v>
+        <v>165000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-37,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2494,60 +2494,60 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>229675</v>
+        <v>167000</v>
       </c>
       <c r="K34" t="n">
-        <v>429675</v>
+        <v>165000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-09-03_00992A_full_holdings.xlsx</t>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2562,55 +2562,55 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>177000</v>
+        <v>629000</v>
       </c>
       <c r="K35" t="n">
-        <v>277000</v>
+        <v>637000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2630,50 +2630,50 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>513000</v>
+        <v>198000</v>
       </c>
       <c r="K36" t="n">
-        <v>441000</v>
+        <v>200000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-72,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2683,60 +2683,60 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>595000</v>
+        <v>131000</v>
       </c>
       <c r="K37" t="n">
-        <v>485000</v>
+        <v>134000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-110,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2746,60 +2746,60 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.73%</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>979000</v>
+        <v>315000</v>
       </c>
       <c r="K38" t="n">
-        <v>696000</v>
+        <v>327000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-283,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2809,53 +2809,53 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>12000</v>
+        <v>107000</v>
       </c>
       <c r="K39" t="n">
-        <v>49000</v>
+        <v>105000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>37,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -2867,37 +2867,55 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6510</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>3042</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>晶技</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>精測</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>晶技</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.54%</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>0.34%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>192000</v>
+      </c>
       <c r="K40" t="n">
-        <v>16000</v>
-      </c>
-      <c r="L40" t="inlineStr"/>
+        <v>196000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>2026-09-03_00993A_full_holdings.xlsx</t>
@@ -2922,43 +2940,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>1613000</v>
+        <v>88000</v>
       </c>
       <c r="K41" t="n">
-        <v>1669000</v>
+        <v>90000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>56,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2980,48 +2998,48 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>1276000</v>
+        <v>46000</v>
       </c>
       <c r="K42" t="n">
-        <v>1241000</v>
+        <v>47000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-35,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3048,43 +3066,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>161000</v>
+        <v>939000</v>
       </c>
       <c r="K43" t="n">
-        <v>165000</v>
+        <v>953000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>14,000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3106,48 +3124,48 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>167000</v>
+        <v>556000</v>
       </c>
       <c r="K44" t="n">
-        <v>165000</v>
+        <v>564000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3169,48 +3187,48 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>629000</v>
+        <v>23000</v>
       </c>
       <c r="K45" t="n">
-        <v>637000</v>
+        <v>22000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3237,43 +3255,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>198000</v>
+        <v>352000</v>
       </c>
       <c r="K46" t="n">
-        <v>200000</v>
+        <v>359000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3300,43 +3318,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>1.88%</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>131000</v>
+        <v>390000</v>
       </c>
       <c r="K47" t="n">
-        <v>134000</v>
+        <v>401000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>11,000</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3358,48 +3376,48 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>信驊科技</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>信驊科技</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>2.81%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.76%</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>315000</v>
+        <v>20600</v>
       </c>
       <c r="K48" t="n">
-        <v>327000</v>
+        <v>15600</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>-5,000</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3421,48 +3439,48 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>107000</v>
+        <v>163000</v>
       </c>
       <c r="K49" t="n">
-        <v>105000</v>
+        <v>165000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3489,43 +3507,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>192000</v>
+        <v>90000</v>
       </c>
       <c r="K50" t="n">
-        <v>196000</v>
+        <v>93000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3547,48 +3565,48 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>2.34%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>88000</v>
+        <v>34000</v>
       </c>
       <c r="K51" t="n">
-        <v>90000</v>
+        <v>32000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3610,48 +3628,48 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>46000</v>
+        <v>140191</v>
       </c>
       <c r="K52" t="n">
-        <v>47000</v>
+        <v>134191</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3678,43 +3696,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>勤誠興業</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>勤誠興業</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>939000</v>
+        <v>67000</v>
       </c>
       <c r="K53" t="n">
-        <v>953000</v>
+        <v>68000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3741,27 +3759,27 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3770,647 +3788,17 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>556000</v>
+        <v>122000</v>
       </c>
       <c r="K54" t="n">
-        <v>564000</v>
+        <v>128000</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
-        <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>1.30%</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>1.25%</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>23000</v>
-      </c>
-      <c r="K55" t="n">
-        <v>22000</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>-1,000</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>3702</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>大聯大</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>大聯大</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>0.35%</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>0.37%</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>352000</v>
-      </c>
-      <c r="K56" t="n">
-        <v>359000</v>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>7,000</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>4958</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>1.93%</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>1.88%</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>390000</v>
-      </c>
-      <c r="K57" t="n">
-        <v>401000</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>11,000</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>信驊科技</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>信驊科技</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>3.57%</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2.81%</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>-0.76%</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>20600</v>
-      </c>
-      <c r="K58" t="n">
-        <v>15600</v>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>-5,000</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>0.44%</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>0.46%</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>163000</v>
-      </c>
-      <c r="K59" t="n">
-        <v>165000</v>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>6415</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>矽力*-KY</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>矽力*-KY</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>0.37%</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>90000</v>
-      </c>
-      <c r="K60" t="n">
-        <v>93000</v>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2.34%</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>2.26%</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>-0.08%</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>34000</v>
-      </c>
-      <c r="K61" t="n">
-        <v>32000</v>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>-2,000</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>3.58%</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>3.35%</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>-0.23%</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>140191</v>
-      </c>
-      <c r="K62" t="n">
-        <v>134191</v>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>-6,000</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>勤誠興業</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>勤誠興業</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>0.63%</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>0.65%</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>67000</v>
-      </c>
-      <c r="K63" t="n">
-        <v>68000</v>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>1.51%</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>1.53%</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>122000</v>
-      </c>
-      <c r="K64" t="n">
-        <v>128000</v>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>6,000</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
         <is>
           <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-09-04_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-04_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,55 +627,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>台灣塑膠工業</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>台灣塑膠工業</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1577000</v>
+        <v>1158000</v>
       </c>
       <c r="K4" t="n">
-        <v>1103000</v>
+        <v>1145000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-474,000</t>
+          <t>-13,000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -685,123 +685,105 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>東元電機</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>東元電機</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3473000</v>
+        <v>103000</v>
       </c>
       <c r="K5" t="n">
-        <v>2904000</v>
+        <v>115000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-569,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>川湖科技</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>川湖科技</t>
-        </is>
-      </c>
+          <t>譜瑞-KY</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.93%</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.13%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-0.80%</t>
-        </is>
-      </c>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>7000</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-6,000</t>
-        </is>
-      </c>
+        <v>16000</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -816,55 +798,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>383000</v>
+        <v>300000</v>
       </c>
       <c r="K7" t="n">
-        <v>295000</v>
+        <v>191000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-88,000</t>
+          <t>-109,000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -879,55 +861,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>138000</v>
+        <v>3100000</v>
       </c>
       <c r="K8" t="n">
-        <v>97000</v>
+        <v>1500000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-41,000</t>
+          <t>-1,600,000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -942,55 +924,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>15.99%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>15.47%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>193000</v>
+        <v>10500000</v>
       </c>
       <c r="K9" t="n">
-        <v>105000</v>
+        <v>10300000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-88,000</t>
+          <t>-200,000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1000,60 +982,60 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>富邦金融控股</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>富邦金融控股</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>154000</v>
+        <v>2000000</v>
       </c>
       <c r="K10" t="n">
-        <v>1004000</v>
+        <v>1000000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>850,000</t>
+          <t>-1,000,000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1063,60 +1045,60 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>中國信託金融控股</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>中國信託金融控股</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>306000</v>
+        <v>5000000</v>
       </c>
       <c r="K11" t="n">
-        <v>2178000</v>
+        <v>1500000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1,872,000</t>
+          <t>-3,500,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1126,60 +1108,60 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16000</v>
+        <v>1351000</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>2000000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-15,000</t>
+          <t>649,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1194,48 +1176,48 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>奇鋐科技</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>奇鋐科技</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>3.69%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>3.39%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.74%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>76000</v>
+        <v>810000</v>
       </c>
       <c r="K13" t="n">
-        <v>52000</v>
+        <v>736000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-24,000</t>
+          <t>-74,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1239,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>台灣塑膠工業</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>台灣塑膠工業</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1277,23 +1259,23 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>31000</v>
+        <v>1577000</v>
       </c>
       <c r="K14" t="n">
-        <v>22000</v>
+        <v>1103000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-9,000</t>
+          <t>-474,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1320,43 +1302,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>穩懋半導體</t>
+          <t>東元電機</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>穩懋半導體</t>
+          <t>東元電機</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>326000</v>
+        <v>3473000</v>
       </c>
       <c r="K15" t="n">
-        <v>203000</v>
+        <v>2904000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-123,000</t>
+          <t>-569,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1383,43 +1365,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>健策精密工業</t>
+          <t>川湖科技</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>健策精密工業</t>
+          <t>川湖科技</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.50%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>27000</v>
+        <v>7000</v>
       </c>
       <c r="K16" t="n">
-        <v>18000</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-9,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1446,43 +1428,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>貿聯控股（BizLink Holding In</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>貿聯控股（BizLink Holding In</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>105000</v>
+        <v>383000</v>
       </c>
       <c r="K17" t="n">
-        <v>94000</v>
+        <v>295000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-11,000</t>
+          <t>-88,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1504,48 +1486,48 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>日月光投資控股</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>日月光投資控股</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.81%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.01%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>435000</v>
+        <v>138000</v>
       </c>
       <c r="K18" t="n">
-        <v>706000</v>
+        <v>97000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>271,000</t>
+          <t>-41,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1572,43 +1554,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>110000</v>
+        <v>193000</v>
       </c>
       <c r="K19" t="n">
-        <v>77000</v>
+        <v>105000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-33,000</t>
+          <t>-88,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1635,43 +1617,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>光紅建聖</t>
+          <t>富邦金融控股</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>光紅建聖</t>
+          <t>富邦金融控股</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>+1.12%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>74000</v>
+        <v>154000</v>
       </c>
       <c r="K20" t="n">
-        <v>140000</v>
+        <v>1004000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>850,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1693,48 +1675,48 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>環球晶圓</t>
+          <t>中國信託金融控股</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>環球晶圓</t>
+          <t>中國信託金融控股</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>174000</v>
+        <v>306000</v>
       </c>
       <c r="K21" t="n">
-        <v>143000</v>
+        <v>2178000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-31,000</t>
+          <t>1,872,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1761,43 +1743,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>新代科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>新代科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>108000</v>
+        <v>16000</v>
       </c>
       <c r="K22" t="n">
-        <v>92000</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-16,000</t>
+          <t>-15,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1824,43 +1806,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>高力熱處理工業</t>
+          <t>奇鋐科技</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>高力熱處理工業</t>
+          <t>奇鋐科技</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>-0.74%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>113000</v>
+        <v>76000</v>
       </c>
       <c r="K23" t="n">
-        <v>76000</v>
+        <v>52000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-37,000</t>
+          <t>-24,000</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1872,7 +1854,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1882,60 +1864,60 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>聯亞光電工業</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>聯亞光電工業</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>229675</v>
+        <v>31000</v>
       </c>
       <c r="K24" t="n">
-        <v>429675</v>
+        <v>22000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>-9,000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-09-03_00992A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1945,60 +1927,60 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>穩懋半導體</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>穩懋半導體</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>177000</v>
+        <v>326000</v>
       </c>
       <c r="K25" t="n">
-        <v>277000</v>
+        <v>203000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>-123,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2013,55 +1995,55 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>健策精密工業</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>健策精密工業</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>-0.50%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>513000</v>
+        <v>27000</v>
       </c>
       <c r="K26" t="n">
-        <v>441000</v>
+        <v>18000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-72,000</t>
+          <t>-9,000</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2076,55 +2058,55 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>595000</v>
+        <v>105000</v>
       </c>
       <c r="K27" t="n">
-        <v>485000</v>
+        <v>94000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-110,000</t>
+          <t>-11,000</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2134,60 +2116,60 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>日月光投資控股</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>日月光投資控股</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>4.01%</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>979000</v>
+        <v>435000</v>
       </c>
       <c r="K28" t="n">
-        <v>696000</v>
+        <v>706000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-283,000</t>
+          <t>271,000</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2197,105 +2179,123 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>12000</v>
+        <v>110000</v>
       </c>
       <c r="K29" t="n">
-        <v>49000</v>
+        <v>77000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>37,000</t>
+          <t>-33,000</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6510</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>6442</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>光紅建聖</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>精測</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>光紅建聖</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1.27%</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.54%</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>2.39%</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>+1.12%</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>74000</v>
+      </c>
       <c r="K30" t="n">
-        <v>16000</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
+        <v>140000</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>66,000</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2305,60 +2305,60 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>環球晶圓</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>環球晶圓</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>1613000</v>
+        <v>174000</v>
       </c>
       <c r="K31" t="n">
-        <v>1669000</v>
+        <v>143000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>56,000</t>
+          <t>-31,000</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2373,55 +2373,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>新代科技</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>新代科技</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>2.37%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>1276000</v>
+        <v>108000</v>
       </c>
       <c r="K32" t="n">
-        <v>1241000</v>
+        <v>92000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-35,000</t>
+          <t>-16,000</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2431,60 +2431,60 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>高力熱處理工業</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>高力熱處理工業</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>161000</v>
+        <v>113000</v>
       </c>
       <c r="K33" t="n">
-        <v>165000</v>
+        <v>76000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>-37,000</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2494,60 +2494,60 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>2.61%</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>167000</v>
+        <v>229675</v>
       </c>
       <c r="K34" t="n">
-        <v>165000</v>
+        <v>429675</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+          <t>2026-09-03_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2562,55 +2562,55 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>629000</v>
+        <v>177000</v>
       </c>
       <c r="K35" t="n">
-        <v>637000</v>
+        <v>277000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2630,50 +2630,50 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>198000</v>
+        <v>513000</v>
       </c>
       <c r="K36" t="n">
-        <v>200000</v>
+        <v>441000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>-72,000</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2683,60 +2683,60 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>131000</v>
+        <v>595000</v>
       </c>
       <c r="K37" t="n">
-        <v>134000</v>
+        <v>485000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>-110,000</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2746,60 +2746,60 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.63%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>315000</v>
+        <v>979000</v>
       </c>
       <c r="K38" t="n">
-        <v>327000</v>
+        <v>696000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>-283,000</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2809,53 +2809,53 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>107000</v>
+        <v>12000</v>
       </c>
       <c r="K39" t="n">
-        <v>105000</v>
+        <v>49000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>37,000</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -2867,55 +2867,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3042</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>晶技</t>
-        </is>
-      </c>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>晶技</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>0.34%</t>
-        </is>
-      </c>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.34%</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>192000</v>
-      </c>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="n">
-        <v>196000</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>4,000</t>
-        </is>
-      </c>
+        <v>16000</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>2026-09-03_00993A_full_holdings.xlsx</t>
@@ -2940,43 +2922,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>3.72%</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>88000</v>
+        <v>1613000</v>
       </c>
       <c r="K41" t="n">
-        <v>90000</v>
+        <v>1669000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>56,000</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2998,48 +2980,48 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>46000</v>
+        <v>1276000</v>
       </c>
       <c r="K42" t="n">
-        <v>47000</v>
+        <v>1241000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>-35,000</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3066,43 +3048,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>939000</v>
+        <v>161000</v>
       </c>
       <c r="K43" t="n">
-        <v>953000</v>
+        <v>165000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3124,48 +3106,48 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>556000</v>
+        <v>167000</v>
       </c>
       <c r="K44" t="n">
-        <v>564000</v>
+        <v>165000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3187,48 +3169,48 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>23000</v>
+        <v>629000</v>
       </c>
       <c r="K45" t="n">
-        <v>22000</v>
+        <v>637000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3255,43 +3237,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>352000</v>
+        <v>198000</v>
       </c>
       <c r="K46" t="n">
-        <v>359000</v>
+        <v>200000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3318,43 +3300,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>390000</v>
+        <v>131000</v>
       </c>
       <c r="K47" t="n">
-        <v>401000</v>
+        <v>134000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>11,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3376,48 +3358,48 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>信驊科技</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>信驊科技</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>1.73%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-0.76%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>20600</v>
+        <v>315000</v>
       </c>
       <c r="K48" t="n">
-        <v>15600</v>
+        <v>327000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-5,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3439,48 +3421,48 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>163000</v>
+        <v>107000</v>
       </c>
       <c r="K49" t="n">
-        <v>165000</v>
+        <v>105000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3507,43 +3489,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>90000</v>
+        <v>192000</v>
       </c>
       <c r="K50" t="n">
-        <v>93000</v>
+        <v>196000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3565,48 +3547,48 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>34000</v>
+        <v>88000</v>
       </c>
       <c r="K51" t="n">
-        <v>32000</v>
+        <v>90000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3628,48 +3610,48 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>140191</v>
+        <v>46000</v>
       </c>
       <c r="K52" t="n">
-        <v>134191</v>
+        <v>47000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3696,43 +3678,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>勤誠興業</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>勤誠興業</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>67000</v>
+        <v>939000</v>
       </c>
       <c r="K53" t="n">
-        <v>68000</v>
+        <v>953000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>14,000</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3759,46 +3741,676 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1.27%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>556000</v>
+      </c>
+      <c r="K54" t="n">
+        <v>564000</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>23000</v>
+      </c>
+      <c r="K55" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3702</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>大聯大</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>大聯大</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>352000</v>
+      </c>
+      <c r="K56" t="n">
+        <v>359000</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>1.88%</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>390000</v>
+      </c>
+      <c r="K57" t="n">
+        <v>401000</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>信驊科技</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>信驊科技</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2.81%</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>-0.76%</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>20600</v>
+      </c>
+      <c r="K58" t="n">
+        <v>15600</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>-5,000</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>6239</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>0.44%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>163000</v>
+      </c>
+      <c r="K59" t="n">
+        <v>165000</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>矽力*-KY</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>矽力*-KY</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>90000</v>
+      </c>
+      <c r="K60" t="n">
+        <v>93000</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2.34%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>-0.08%</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>34000</v>
+      </c>
+      <c r="K61" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>3.58%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>3.35%</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>140191</v>
+      </c>
+      <c r="K62" t="n">
+        <v>134191</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>-6,000</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>勤誠興業</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>勤誠興業</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>0.65%</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>67000</v>
+      </c>
+      <c r="K63" t="n">
+        <v>68000</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>8996</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>1.51%</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>1.53%</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>+0.02%</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="J64" t="n">
         <v>122000</v>
       </c>
-      <c r="K54" t="n">
+      <c r="K64" t="n">
         <v>128000</v>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-09-04_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-04_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,52 +738,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>台灣塑膠工業</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>台灣塑膠工業</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.01%</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.70%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-0.30%</t>
+        </is>
+      </c>
       <c r="J6" t="n">
-        <v>16000</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+        <v>1577000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1103000</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-474,000</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-03_00403A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -798,55 +816,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>東元電機</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>東元電機</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>300000</v>
+        <v>3473000</v>
       </c>
       <c r="K7" t="n">
-        <v>191000</v>
+        <v>2904000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-109,000</t>
+          <t>-569,000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-09-03_00403A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -861,55 +879,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>長興</t>
+          <t>川湖科技</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>長興</t>
+          <t>川湖科技</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3100000</v>
+        <v>7000</v>
       </c>
       <c r="K8" t="n">
-        <v>1500000</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-1,600,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-09-03_00403A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -924,55 +942,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>15.99%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>15.47%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>10500000</v>
+        <v>383000</v>
       </c>
       <c r="K9" t="n">
-        <v>10300000</v>
+        <v>295000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-200,000</t>
+          <t>-88,000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-09-03_00403A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -987,55 +1005,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>2.81%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2000000</v>
+        <v>138000</v>
       </c>
       <c r="K10" t="n">
-        <v>1000000</v>
+        <v>97000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-1,000,000</t>
+          <t>-41,000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09-03_00403A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1050,55 +1068,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科技</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>5000000</v>
+        <v>193000</v>
       </c>
       <c r="K11" t="n">
-        <v>1500000</v>
+        <v>105000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-3,500,000</t>
+          <t>-88,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-03_00403A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1113,55 +1131,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>富邦金融控股</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>富邦金融控股</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1351000</v>
+        <v>154000</v>
       </c>
       <c r="K12" t="n">
-        <v>2000000</v>
+        <v>1004000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>649,000</t>
+          <t>850,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-03_00403A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1171,53 +1189,53 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>中國信託金融控股</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>中國信託金融控股</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>810000</v>
+        <v>306000</v>
       </c>
       <c r="K13" t="n">
-        <v>736000</v>
+        <v>2178000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-74,000</t>
+          <t>1,872,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-09-03_00403A_full_holdings.xlsx</t>
+          <t>2026-09-03_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1239,43 +1257,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>台灣塑膠工業</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>台灣塑膠工業</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1577000</v>
+        <v>16000</v>
       </c>
       <c r="K14" t="n">
-        <v>1103000</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-474,000</t>
+          <t>-15,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1302,17 +1320,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>東元電機</t>
+          <t>奇鋐科技</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>東元電機</t>
+          <t>奇鋐科技</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1322,23 +1340,23 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.74%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3473000</v>
+        <v>76000</v>
       </c>
       <c r="K15" t="n">
-        <v>2904000</v>
+        <v>52000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-569,000</t>
+          <t>-24,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1365,43 +1383,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>川湖科技</t>
+          <t>聯亞光電工業</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>川湖科技</t>
+          <t>聯亞光電工業</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>7000</v>
+        <v>31000</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>22000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>-9,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1428,43 +1446,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>穩懋半導體</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>穩懋半導體</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>383000</v>
+        <v>326000</v>
       </c>
       <c r="K17" t="n">
-        <v>295000</v>
+        <v>203000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-88,000</t>
+          <t>-123,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1491,43 +1509,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>健策精密工業</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>健策精密工業</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>-0.50%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>138000</v>
+        <v>27000</v>
       </c>
       <c r="K18" t="n">
-        <v>97000</v>
+        <v>18000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-41,000</t>
+          <t>-9,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1554,43 +1572,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>南亞科技</t>
+          <t>貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>193000</v>
+        <v>105000</v>
       </c>
       <c r="K19" t="n">
-        <v>105000</v>
+        <v>94000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-88,000</t>
+          <t>-11,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1617,43 +1635,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>富邦金融控股</t>
+          <t>日月光投資控股</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>富邦金融控股</t>
+          <t>日月光投資控股</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>4.01%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>154000</v>
+        <v>435000</v>
       </c>
       <c r="K20" t="n">
-        <v>1004000</v>
+        <v>706000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>850,000</t>
+          <t>271,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1675,48 +1693,48 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>中國信託金融控股</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>中國信託金融控股</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>306000</v>
+        <v>110000</v>
       </c>
       <c r="K21" t="n">
-        <v>2178000</v>
+        <v>77000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1,872,000</t>
+          <t>-33,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1738,48 +1756,48 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>光紅建聖</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>光紅建聖</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>2.39%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+1.12%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>16000</v>
+        <v>74000</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>140000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-15,000</t>
+          <t>66,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1806,43 +1824,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>奇鋐科技</t>
+          <t>環球晶圓</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>奇鋐科技</t>
+          <t>環球晶圓</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.74%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>76000</v>
+        <v>174000</v>
       </c>
       <c r="K23" t="n">
-        <v>52000</v>
+        <v>143000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-24,000</t>
+          <t>-31,000</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1869,43 +1887,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>新代科技</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>聯亞光電工業</t>
+          <t>新代科技</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>2.37%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>31000</v>
+        <v>108000</v>
       </c>
       <c r="K24" t="n">
-        <v>22000</v>
+        <v>92000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-9,000</t>
+          <t>-16,000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1932,22 +1950,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>穩懋半導體</t>
+          <t>高力熱處理工業</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>穩懋半導體</t>
+          <t>高力熱處理工業</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,18 +1975,18 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>326000</v>
+        <v>113000</v>
       </c>
       <c r="K25" t="n">
-        <v>203000</v>
+        <v>76000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-123,000</t>
+          <t>-37,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1980,7 +1998,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1990,60 +2008,60 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>健策精密工業</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>健策精密工業</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>2.61%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-0.50%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>27000</v>
+        <v>229675</v>
       </c>
       <c r="K26" t="n">
-        <v>18000</v>
+        <v>429675</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-9,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2053,60 +2071,60 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>貿聯控股（BizLink Holding In</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>貿聯控股（BizLink Holding In</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>105000</v>
+        <v>177000</v>
       </c>
       <c r="K27" t="n">
-        <v>94000</v>
+        <v>277000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-11,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2116,60 +2134,60 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>日月光投資控股</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>日月光投資控股</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.01%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>435000</v>
+        <v>513000</v>
       </c>
       <c r="K28" t="n">
-        <v>706000</v>
+        <v>441000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>271,000</t>
+          <t>-72,000</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2184,55 +2202,55 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>110000</v>
+        <v>595000</v>
       </c>
       <c r="K29" t="n">
-        <v>77000</v>
+        <v>485000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-33,000</t>
+          <t>-110,000</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2242,60 +2260,60 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>光紅建聖</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>光紅建聖</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>+1.12%</t>
+          <t>-0.63%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>74000</v>
+        <v>979000</v>
       </c>
       <c r="K30" t="n">
-        <v>140000</v>
+        <v>696000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>-283,000</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2305,123 +2323,105 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>環球晶圓</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>環球晶圓</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>174000</v>
+        <v>12000</v>
       </c>
       <c r="K31" t="n">
-        <v>143000</v>
+        <v>49000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-31,000</t>
+          <t>37,000</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7750</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>新代科技</t>
-        </is>
-      </c>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>新代科技</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2.37%</t>
-        </is>
-      </c>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.95%</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>-0.42%</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>108000</v>
-      </c>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
-        <v>92000</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>-16,000</t>
-        </is>
-      </c>
+        <v>16000</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2431,60 +2431,60 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>高力熱處理工業</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>高力熱處理工業</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>3.72%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>113000</v>
+        <v>1613000</v>
       </c>
       <c r="K33" t="n">
-        <v>76000</v>
+        <v>1669000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-37,000</t>
+          <t>56,000</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-03_00985A_full_holdings.xlsx</t>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2494,60 +2494,60 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>229675</v>
+        <v>1276000</v>
       </c>
       <c r="K34" t="n">
-        <v>429675</v>
+        <v>1241000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>-35,000</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-09-03_00992A_full_holdings.xlsx</t>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2562,55 +2562,55 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>177000</v>
+        <v>161000</v>
       </c>
       <c r="K35" t="n">
-        <v>277000</v>
+        <v>165000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2625,55 +2625,55 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>513000</v>
+        <v>167000</v>
       </c>
       <c r="K36" t="n">
-        <v>441000</v>
+        <v>165000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-72,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2683,60 +2683,60 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>595000</v>
+        <v>629000</v>
       </c>
       <c r="K37" t="n">
-        <v>485000</v>
+        <v>637000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-110,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2746,60 +2746,60 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>979000</v>
+        <v>198000</v>
       </c>
       <c r="K38" t="n">
-        <v>696000</v>
+        <v>200000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-283,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2814,48 +2814,48 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>12000</v>
+        <v>131000</v>
       </c>
       <c r="K39" t="n">
-        <v>49000</v>
+        <v>134000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>37,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09-03_00407A_full_holdings.xlsx</t>
+          <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -2867,37 +2867,55 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6510</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>2455</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>精測</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.54%</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>1.73%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>+0.06%</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>315000</v>
+      </c>
       <c r="K40" t="n">
-        <v>16000</v>
-      </c>
-      <c r="L40" t="inlineStr"/>
+        <v>327000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>2026-09-03_00993A_full_holdings.xlsx</t>
@@ -2917,48 +2935,48 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>1613000</v>
+        <v>107000</v>
       </c>
       <c r="K41" t="n">
-        <v>1669000</v>
+        <v>105000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>56,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2980,32 +2998,32 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3014,14 +3032,14 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>1276000</v>
+        <v>192000</v>
       </c>
       <c r="K42" t="n">
-        <v>1241000</v>
+        <v>196000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-35,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3048,43 +3066,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>161000</v>
+        <v>88000</v>
       </c>
       <c r="K43" t="n">
-        <v>165000</v>
+        <v>90000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3106,48 +3124,48 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>167000</v>
+        <v>46000</v>
       </c>
       <c r="K44" t="n">
-        <v>165000</v>
+        <v>47000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3174,43 +3192,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>629000</v>
+        <v>939000</v>
       </c>
       <c r="K45" t="n">
-        <v>637000</v>
+        <v>953000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>14,000</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3237,43 +3255,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>198000</v>
+        <v>556000</v>
       </c>
       <c r="K46" t="n">
-        <v>200000</v>
+        <v>564000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3295,48 +3313,48 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>131000</v>
+        <v>23000</v>
       </c>
       <c r="K47" t="n">
-        <v>134000</v>
+        <v>22000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3363,43 +3381,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>315000</v>
+        <v>352000</v>
       </c>
       <c r="K48" t="n">
-        <v>327000</v>
+        <v>359000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3421,48 +3439,48 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>1.88%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>107000</v>
+        <v>390000</v>
       </c>
       <c r="K49" t="n">
-        <v>105000</v>
+        <v>401000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>11,000</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3484,48 +3502,48 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>信驊科技</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>信驊科技</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>2.81%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.76%</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>192000</v>
+        <v>20600</v>
       </c>
       <c r="K50" t="n">
-        <v>196000</v>
+        <v>15600</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>-5,000</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3552,39 +3570,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>88000</v>
+        <v>163000</v>
       </c>
       <c r="K51" t="n">
-        <v>90000</v>
+        <v>165000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3615,43 +3633,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>46000</v>
+        <v>90000</v>
       </c>
       <c r="K52" t="n">
-        <v>47000</v>
+        <v>93000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3673,48 +3691,48 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>2.34%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>939000</v>
+        <v>34000</v>
       </c>
       <c r="K53" t="n">
-        <v>953000</v>
+        <v>32000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3736,48 +3754,48 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>556000</v>
+        <v>140191</v>
       </c>
       <c r="K54" t="n">
-        <v>564000</v>
+        <v>134191</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3799,48 +3817,48 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>勤誠興業</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>勤誠興業</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>23000</v>
+        <v>67000</v>
       </c>
       <c r="K55" t="n">
-        <v>22000</v>
+        <v>68000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3867,27 +3885,27 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3896,521 +3914,17 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>352000</v>
+        <v>122000</v>
       </c>
       <c r="K56" t="n">
-        <v>359000</v>
+        <v>128000</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
-        <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>4958</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>1.93%</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>1.88%</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>390000</v>
-      </c>
-      <c r="K57" t="n">
-        <v>401000</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>11,000</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>信驊科技</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>信驊科技</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>3.57%</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2.81%</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>-0.76%</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>20600</v>
-      </c>
-      <c r="K58" t="n">
-        <v>15600</v>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>-5,000</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>0.44%</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>0.46%</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>163000</v>
-      </c>
-      <c r="K59" t="n">
-        <v>165000</v>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>6415</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>矽力*-KY</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>矽力*-KY</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>0.37%</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>90000</v>
-      </c>
-      <c r="K60" t="n">
-        <v>93000</v>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2.34%</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>2.26%</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>-0.08%</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>34000</v>
-      </c>
-      <c r="K61" t="n">
-        <v>32000</v>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>-2,000</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>3.58%</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>3.35%</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>-0.23%</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>140191</v>
-      </c>
-      <c r="K62" t="n">
-        <v>134191</v>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>-6,000</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>勤誠興業</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>勤誠興業</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>0.63%</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>0.65%</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>67000</v>
-      </c>
-      <c r="K63" t="n">
-        <v>68000</v>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>2026-09-03_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>1.51%</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>1.53%</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>122000</v>
-      </c>
-      <c r="K64" t="n">
-        <v>128000</v>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>6,000</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
         <is>
           <t>2026-09-03_00993A_full_holdings.xlsx</t>
         </is>
